--- a/matrix_size_J200_enercut_enermax.xlsx
+++ b/matrix_size_J200_enercut_enermax.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryanm\OneDrive\Desktop\Research\HOPO-Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92FA08A1-A361-443B-BE67-B17D2FBB156D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A1E8090-CDF1-4948-8151-772130BE3CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{3D1FC524-8C97-4DCA-8D2D-8A8A36B25BF5}"/>
   </bookViews>
